--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:19</t>
+    <t xml:space="preserve">2026-10-05 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -671,7 +671,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2071883.62</v>
+        <v>2071883.63</v>
       </c>
     </row>
     <row r="5">
@@ -688,7 +688,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2031121.12</v>
+        <v>2031121.13</v>
       </c>
     </row>
     <row r="6">
@@ -722,7 +722,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1821095.62</v>
+        <v>1821095.63</v>
       </c>
     </row>
     <row r="8">
@@ -739,7 +739,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1498330.12</v>
+        <v>1498330.13</v>
       </c>
     </row>
     <row r="9">
@@ -756,7 +756,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1455922.12</v>
+        <v>1455922.13</v>
       </c>
     </row>
     <row r="10">
@@ -807,7 +807,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1176513.12</v>
+        <v>1176513.13</v>
       </c>
     </row>
     <row r="13">
@@ -994,7 +994,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1049512.62</v>
+        <v>1049512.63</v>
       </c>
     </row>
     <row r="24">
@@ -1011,7 +1011,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1049025.62</v>
+        <v>1049025.63</v>
       </c>
     </row>
     <row r="25">
@@ -1147,7 +1147,7 @@
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>962168.12</v>
+        <v>962168.13</v>
       </c>
     </row>
     <row r="33">
